--- a/datasets/knitting/inventory-brightway.xlsx
+++ b/datasets/knitting/inventory-brightway.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentcarrieres/carbonfact/lca/lca/notebooks/science/Vincent/Carbonfact database/Knitting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1C83A3-9A79-CA4B-9B1E-357F23B8C466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B352E2-936F-FF4F-8E20-6080A9BCA088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3680" yWindow="-21040" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4540" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="63">
   <si>
     <t>Database</t>
   </si>
@@ -85,7 +85,7 @@
     <t>electricity, medium voltage</t>
   </si>
   <si>
-    <t>kilowatt hour</t>
+    <t>kWh</t>
   </si>
   <si>
     <t>technosphere</t>
@@ -94,7 +94,7 @@
     <t>ecoinvent-3.12-cutoff</t>
   </si>
   <si>
-    <t>lubricating oil production</t>
+    <t>market for lubricating oil</t>
   </si>
   <si>
     <t>lubricating oil</t>
@@ -109,6 +109,9 @@
     <t>waste mineral oil</t>
   </si>
   <si>
+    <t>kg</t>
+  </si>
+  <si>
     <t>market for building machine</t>
   </si>
   <si>
@@ -127,9 +130,6 @@
     <t>building, hall</t>
   </si>
   <si>
-    <t>square meter</t>
-  </si>
-  <si>
     <t>treatment of waste electric and electronic equipment, shredding</t>
   </si>
   <si>
@@ -178,6 +178,9 @@
     <t>knitted fabric, circular, 370 dtex</t>
   </si>
   <si>
+    <t>Circular Knitting, 45 dtex</t>
+  </si>
+  <si>
     <t>knitted fabric, circular, 45 dtex</t>
   </si>
   <si>
@@ -205,7 +208,7 @@
     <t>knitted fabric, seamless, average</t>
   </si>
   <si>
-    <t>Circular Knitting, 45 dtex</t>
+    <t>m2</t>
   </si>
 </sst>
 </file>
@@ -549,6 +552,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -721,7 +725,7 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
         <v>22</v>
@@ -732,13 +736,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -755,19 +759,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
         <v>22</v>
@@ -778,19 +782,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <v>1.3899999999999999E-4</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
         <v>22</v>
@@ -813,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G18" t="s">
         <v>22</v>
@@ -984,7 +988,7 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G31" t="s">
         <v>22</v>
@@ -995,13 +999,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -1018,19 +1022,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G33" t="s">
         <v>22</v>
@@ -1041,19 +1045,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
         <v>22</v>
@@ -1076,7 +1080,7 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G35" t="s">
         <v>22</v>
@@ -1247,7 +1251,7 @@
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G48" t="s">
         <v>22</v>
@@ -1258,13 +1262,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
@@ -1281,19 +1285,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B50">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
         <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G50" t="s">
         <v>22</v>
@@ -1304,19 +1308,19 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G51" t="s">
         <v>22</v>
@@ -1339,7 +1343,7 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G52" t="s">
         <v>22</v>
@@ -1510,7 +1514,7 @@
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G65" t="s">
         <v>22</v>
@@ -1521,13 +1525,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B66">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66" t="s">
         <v>9</v>
@@ -1544,19 +1548,19 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B67">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G67" t="s">
         <v>22</v>
@@ -1567,19 +1571,19 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B68">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G68" t="s">
         <v>22</v>
@@ -1602,7 +1606,7 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G69" t="s">
         <v>22</v>
@@ -1773,7 +1777,7 @@
         <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G82" t="s">
         <v>22</v>
@@ -1784,13 +1788,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B83">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
@@ -1807,19 +1811,19 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B84">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G84" t="s">
         <v>22</v>
@@ -1830,19 +1834,19 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B85">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G85" t="s">
         <v>22</v>
@@ -1865,7 +1869,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G86" t="s">
         <v>22</v>
@@ -2036,7 +2040,7 @@
         <v>26</v>
       </c>
       <c r="E99" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G99" t="s">
         <v>22</v>
@@ -2047,13 +2051,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B100">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
@@ -2070,19 +2074,19 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B101">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D101" t="s">
         <v>26</v>
       </c>
       <c r="E101" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G101" t="s">
         <v>22</v>
@@ -2093,19 +2097,19 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B102">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D102" t="s">
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G102" t="s">
         <v>22</v>
@@ -2128,7 +2132,7 @@
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G103" t="s">
         <v>22</v>
@@ -2299,7 +2303,7 @@
         <v>26</v>
       </c>
       <c r="E116" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G116" t="s">
         <v>22</v>
@@ -2310,13 +2314,13 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B117">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C117" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
@@ -2333,19 +2337,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B118">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C118" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D118" t="s">
         <v>26</v>
       </c>
       <c r="E118" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G118" t="s">
         <v>22</v>
@@ -2356,19 +2360,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B119">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C119" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D119" t="s">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G119" t="s">
         <v>22</v>
@@ -2391,7 +2395,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G120" t="s">
         <v>22</v>
@@ -2562,7 +2566,7 @@
         <v>26</v>
       </c>
       <c r="E133" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G133" t="s">
         <v>22</v>
@@ -2573,13 +2577,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B134">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s">
         <v>9</v>
@@ -2596,19 +2600,19 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B135">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C135" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D135" t="s">
         <v>26</v>
       </c>
       <c r="E135" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G135" t="s">
         <v>22</v>
@@ -2619,19 +2623,19 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B136">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C136" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D136" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G136" t="s">
         <v>22</v>
@@ -2654,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G137" t="s">
         <v>22</v>
@@ -2668,7 +2672,7 @@
         <v>2</v>
       </c>
       <c r="B139" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
@@ -2689,7 +2693,7 @@
         <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
@@ -2744,13 +2748,13 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
@@ -2825,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="E150" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G150" t="s">
         <v>22</v>
@@ -2836,13 +2840,13 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B151">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C151" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
@@ -2859,19 +2863,19 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B152">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C152" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D152" t="s">
         <v>26</v>
       </c>
       <c r="E152" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G152" t="s">
         <v>22</v>
@@ -2882,19 +2886,19 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B153">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C153" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D153" t="s">
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G153" t="s">
         <v>22</v>
@@ -2917,7 +2921,7 @@
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G154" t="s">
         <v>22</v>
@@ -2931,7 +2935,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
@@ -2952,7 +2956,7 @@
         <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
@@ -3007,13 +3011,13 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
@@ -3088,7 +3092,7 @@
         <v>26</v>
       </c>
       <c r="E167" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G167" t="s">
         <v>22</v>
@@ -3099,13 +3103,13 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B168">
         <v>4.6400000000000003E-7</v>
       </c>
       <c r="C168" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D168" t="s">
         <v>9</v>
@@ -3122,19 +3126,19 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B169">
         <v>-1.1000000000000001E-3</v>
       </c>
       <c r="C169" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D169" t="s">
         <v>26</v>
       </c>
       <c r="E169" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G169" t="s">
         <v>22</v>
@@ -3145,19 +3149,19 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B170">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C170" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G170" t="s">
         <v>22</v>
@@ -3180,7 +3184,7 @@
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G171" t="s">
         <v>22</v>
@@ -3194,7 +3198,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
@@ -3215,7 +3219,7 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
@@ -3270,13 +3274,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
@@ -3351,7 +3355,7 @@
         <v>26</v>
       </c>
       <c r="E184" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G184" t="s">
         <v>22</v>
@@ -3362,13 +3366,13 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B185">
         <v>4.6699999999999999E-7</v>
       </c>
       <c r="C185" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
@@ -3385,19 +3389,19 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B186">
         <v>-2.9999999999999997E-4</v>
       </c>
       <c r="C186" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D186" t="s">
         <v>26</v>
       </c>
       <c r="E186" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G186" t="s">
         <v>22</v>
@@ -3408,19 +3412,19 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B187">
         <v>4.86E-4</v>
       </c>
       <c r="C187" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D187" t="s">
         <v>9</v>
       </c>
       <c r="E187" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G187" t="s">
         <v>22</v>
@@ -3443,7 +3447,7 @@
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G188" t="s">
         <v>22</v>
@@ -3457,7 +3461,7 @@
         <v>2</v>
       </c>
       <c r="B190" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
@@ -3478,7 +3482,7 @@
         <v>6</v>
       </c>
       <c r="B193" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
@@ -3533,13 +3537,13 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D198" t="s">
         <v>9</v>
@@ -3614,7 +3618,7 @@
         <v>26</v>
       </c>
       <c r="E201" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G201" t="s">
         <v>22</v>
@@ -3625,13 +3629,13 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B202">
         <v>1.33E-6</v>
       </c>
       <c r="C202" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D202" t="s">
         <v>9</v>
@@ -3648,19 +3652,19 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B203">
         <v>-3.5E-4</v>
       </c>
       <c r="C203" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D203" t="s">
         <v>26</v>
       </c>
       <c r="E203" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G203" t="s">
         <v>22</v>
@@ -3671,19 +3675,19 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B204">
         <v>1.6099999999999998E-5</v>
       </c>
       <c r="C204" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D204" t="s">
         <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G204" t="s">
         <v>22</v>
@@ -3706,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G205" t="s">
         <v>22</v>
@@ -3720,7 +3724,7 @@
         <v>2</v>
       </c>
       <c r="B207" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
@@ -3741,7 +3745,7 @@
         <v>6</v>
       </c>
       <c r="B210" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
@@ -3796,13 +3800,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B215">
         <v>1</v>
       </c>
       <c r="C215" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D215" t="s">
         <v>9</v>
@@ -3877,7 +3881,7 @@
         <v>26</v>
       </c>
       <c r="E218" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G218" t="s">
         <v>22</v>
@@ -3888,13 +3892,13 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B219">
         <v>5.3300000000000002E-7</v>
       </c>
       <c r="C219" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D219" t="s">
         <v>9</v>
@@ -3911,19 +3915,19 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B220">
         <v>-2.9999999999999997E-4</v>
       </c>
       <c r="C220" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D220" t="s">
         <v>26</v>
       </c>
       <c r="E220" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G220" t="s">
         <v>22</v>
@@ -3934,19 +3938,19 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B221">
         <v>1.6099999999999998E-5</v>
       </c>
       <c r="C221" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D221" t="s">
         <v>9</v>
       </c>
       <c r="E221" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G221" t="s">
         <v>22</v>
@@ -3969,7 +3973,7 @@
         <v>9</v>
       </c>
       <c r="E222" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G222" t="s">
         <v>22</v>
